--- a/VerveStacks_MYS_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_MYS_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39581161-AA9E-4F89-ACDC-82D1A61D36BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C1340A-0291-4E48-9057-8B2CFD4A5AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4424,7 +4424,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74256D4F-661D-491B-8482-4DA6705A15FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{277F9330-BC8C-4825-8465-7B6461A62667}">
   <dimension ref="B3:I176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
